--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -1694,7 +1694,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="652">
   <si>
     <t>Property</t>
   </si>
@@ -897,112 +897,115 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>Observation.category:laboratory</t>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表から"laboratory"を設定する。</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「furst」固定とする。  
+(social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
+  </si>
+  <si>
+    <t>Observation.category:first.id</t>
+  </si>
+  <si>
+    <t>Observation.category:first.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「laboratory」固定とする。</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表を使用する。</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>検体検査を表すコード laboratory を設定する。</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
     <t>laboratory</t>
   </si>
   <si>
-    <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表から"laboratory"を設定する。</t>
-  </si>
-  <si>
-    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「laboratory」固定とする。  
-(social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.id</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「laboratory」固定とする。</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
-  </si>
-  <si>
-    <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表を使用する。</t>
-  </si>
-  <si>
-    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
-  </si>
-  <si>
-    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
-  </si>
-  <si>
-    <t>検体検査を表すコード laboratory を設定する。</t>
-  </si>
-  <si>
-    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -1012,7 +1015,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.display</t>
+    <t>Observation.category:first.coding.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -1036,7 +1039,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.userSelected</t>
+    <t>Observation.category:first.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -1067,7 +1070,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.text</t>
+    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -2386,7 +2389,7 @@
   <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.2265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -6692,7 +6695,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6734,7 +6737,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6755,10 +6758,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6769,10 +6772,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6798,14 +6801,14 @@
         <v>162</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6854,7 +6857,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6875,10 +6878,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6889,10 +6892,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6915,19 +6918,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6976,7 +6979,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6997,10 +7000,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -7011,7 +7014,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>273</v>
@@ -7133,14 +7136,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7162,16 +7165,16 @@
         <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7199,10 +7202,10 @@
         <v>118</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7220,7 +7223,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -7235,30 +7238,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7373,10 +7376,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7493,10 +7496,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7525,10 +7528,10 @@
         <v>288</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>269</v>
@@ -7615,10 +7618,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7733,10 +7736,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7853,10 +7856,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7882,13 +7885,13 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>299</v>
@@ -7975,10 +7978,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8010,7 +8013,7 @@
         <v>307</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8095,10 +8098,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8124,13 +8127,13 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>315</v>
@@ -8182,7 +8185,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8203,10 +8206,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8217,10 +8220,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8246,16 +8249,16 @@
         <v>162</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8304,7 +8307,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8325,10 +8328,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8339,10 +8342,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8365,19 +8368,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8426,7 +8429,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8447,10 +8450,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8461,10 +8464,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8493,10 +8496,10 @@
         <v>274</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O51" t="s" s="2">
         <v>277</v>
@@ -8583,10 +8586,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8609,19 +8612,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8670,7 +8673,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8685,19 +8688,19 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8705,10 +8708,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8731,16 +8734,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8790,7 +8793,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8811,13 +8814,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8825,14 +8828,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8851,19 +8854,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8912,7 +8915,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8927,19 +8930,19 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8947,14 +8950,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8973,19 +8976,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9034,7 +9037,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9049,19 +9052,19 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9069,10 +9072,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9095,16 +9098,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9154,7 +9157,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9175,13 +9178,13 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9189,10 +9192,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9215,19 +9218,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9276,7 +9279,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9291,19 +9294,19 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9311,10 +9314,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9337,19 +9340,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9386,17 +9389,17 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9405,7 +9408,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9414,30 +9417,30 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>83</v>
@@ -9459,19 +9462,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9520,7 +9523,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9529,7 +9532,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9538,30 +9541,30 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
@@ -9586,16 +9589,16 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9644,7 +9647,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9653,7 +9656,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9662,30 +9665,30 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>83</v>
@@ -9710,16 +9713,16 @@
         <v>162</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9768,7 +9771,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9777,7 +9780,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9786,27 +9789,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9832,16 +9835,16 @@
         <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9869,10 +9872,10 @@
         <v>189</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9890,7 +9893,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9899,7 +9902,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9914,7 +9917,7 @@
         <v>137</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9925,14 +9928,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9954,16 +9957,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9991,10 +9994,10 @@
         <v>189</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -10012,7 +10015,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10030,27 +10033,27 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10073,19 +10076,19 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10134,7 +10137,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10155,10 +10158,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10169,10 +10172,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10287,10 +10290,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10407,10 +10410,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10433,16 +10436,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10492,7 +10495,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10516,7 +10519,7 @@
         <v>137</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10527,10 +10530,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10553,13 +10556,13 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10610,7 +10613,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10634,7 +10637,7 @@
         <v>137</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10645,10 +10648,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10671,16 +10674,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10730,7 +10733,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -10754,7 +10757,7 @@
         <v>137</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10765,10 +10768,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10794,13 +10797,13 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10826,13 +10829,13 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10850,7 +10853,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10868,27 +10871,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10914,16 +10917,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10948,13 +10951,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10972,7 +10975,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10993,10 +10996,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11007,10 +11010,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11033,16 +11036,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11092,7 +11095,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11110,27 +11113,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11153,16 +11156,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11212,7 +11215,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11230,27 +11233,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11273,19 +11276,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11334,7 +11337,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11346,7 +11349,7 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
@@ -11355,10 +11358,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11369,10 +11372,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11487,10 +11490,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11607,14 +11610,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11636,10 +11639,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -11694,7 +11697,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11729,10 +11732,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11755,16 +11758,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11814,7 +11817,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11823,7 +11826,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11835,10 +11838,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11849,10 +11852,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11875,16 +11878,16 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11934,7 +11937,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11943,7 +11946,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11955,10 +11958,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11969,10 +11972,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11998,16 +12001,16 @@
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12035,10 +12038,10 @@
         <v>118</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12056,7 +12059,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12074,13 +12077,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12091,10 +12094,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12120,16 +12123,16 @@
         <v>184</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12154,13 +12157,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12178,7 +12181,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12196,13 +12199,13 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12213,10 +12216,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12239,19 +12242,19 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12300,7 +12303,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12324,7 +12327,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12335,10 +12338,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12364,13 +12367,13 @@
         <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12420,7 +12423,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12441,10 +12444,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12455,10 +12458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12481,16 +12484,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12540,7 +12543,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12561,10 +12564,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12575,10 +12578,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12601,16 +12604,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12660,7 +12663,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12681,10 +12684,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12695,10 +12698,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12721,19 +12724,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12782,7 +12785,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12803,10 +12806,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12817,10 +12820,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12935,10 +12938,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13055,14 +13058,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13084,10 +13087,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>143</v>
@@ -13142,7 +13145,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13177,10 +13180,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13206,16 +13209,16 @@
         <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13240,13 +13243,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13264,7 +13267,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13282,16 +13285,16 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -13299,10 +13302,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13325,19 +13328,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13386,7 +13389,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13404,27 +13407,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13450,16 +13453,16 @@
         <v>184</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13487,10 +13490,10 @@
         <v>189</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13508,7 +13511,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13517,7 +13520,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13532,7 +13535,7 @@
         <v>137</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13543,14 +13546,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13572,16 +13575,16 @@
         <v>184</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13609,10 +13612,10 @@
         <v>189</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13630,7 +13633,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13648,27 +13651,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13694,16 +13697,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13752,7 +13755,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13773,10 +13776,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -566,7 +566,7 @@
     <t>Observation.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
     <t>この識別子の目的。</t>
@@ -575,13 +575,13 @@
     <t>アプリケーションは、identifierが一時的であると明示的に述べられない限り、永続的であると想定できる。</t>
   </si>
   <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -600,22 +600,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -630,16 +630,16 @@
     <t>Observation.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -660,7 +660,7 @@
     <t>システムのコンテキスト内で一意の識別子となる文字列を設定。</t>
   </si>
   <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -682,7 +682,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -704,10 +704,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -1769,7 +1769,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -2413,7 +2413,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -829,10 +829,13 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
 </t>
   </si>
   <si>
@@ -908,6 +911,9 @@
   <si>
     <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「furst」固定とする。  
 (social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -5155,15 +5161,17 @@
       <c r="X23" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y23" s="2"/>
+      <c r="Y23" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5197,10 +5205,10 @@
         <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
@@ -5208,10 +5216,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5326,10 +5334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5446,10 +5454,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5472,19 +5480,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5533,7 +5541,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5554,10 +5562,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5568,10 +5576,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5597,16 +5605,16 @@
         <v>162</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5655,7 +5663,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5676,10 +5684,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5690,13 +5698,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>255</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5706,7 +5714,7 @@
         <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>
@@ -5721,13 +5729,13 @@
         <v>184</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>258</v>
@@ -5759,7 +5767,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5801,10 +5809,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5812,10 +5820,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5930,10 +5938,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6050,10 +6058,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6061,10 +6069,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -6076,19 +6084,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -6137,7 +6145,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6158,10 +6166,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6172,10 +6180,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6290,10 +6298,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6410,10 +6418,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6439,23 +6447,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6497,7 +6505,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6518,10 +6526,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6532,10 +6540,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6561,13 +6569,13 @@
         <v>162</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6617,7 +6625,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6638,10 +6646,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6652,10 +6660,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6681,21 +6689,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6737,7 +6745,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6758,10 +6766,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6772,10 +6780,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6801,14 +6809,14 @@
         <v>162</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6857,7 +6865,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6878,10 +6886,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6892,10 +6900,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6918,19 +6926,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6979,7 +6987,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7000,10 +7008,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -7014,10 +7022,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7043,16 +7051,16 @@
         <v>162</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7101,7 +7109,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7122,10 +7130,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -7136,14 +7144,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7165,16 +7173,16 @@
         <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7202,10 +7210,10 @@
         <v>118</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7223,7 +7231,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -7238,30 +7246,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7376,10 +7384,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7496,10 +7504,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7522,19 +7530,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7583,7 +7591,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7604,10 +7612,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7618,10 +7626,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7736,10 +7744,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7856,10 +7864,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7885,16 +7893,16 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7943,7 +7951,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7964,10 +7972,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7978,10 +7986,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8007,13 +8015,13 @@
         <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8063,7 +8071,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8084,10 +8092,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8098,10 +8106,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8127,16 +8135,16 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8185,7 +8193,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8206,10 +8214,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8220,10 +8228,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8249,16 +8257,16 @@
         <v>162</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8307,7 +8315,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8328,10 +8336,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8342,10 +8350,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8368,19 +8376,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8429,7 +8437,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8450,10 +8458,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8464,10 +8472,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8493,16 +8501,16 @@
         <v>162</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8551,7 +8559,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8572,10 +8580,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8586,10 +8594,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8612,19 +8620,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8673,7 +8681,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8688,19 +8696,19 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8708,10 +8716,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8734,16 +8742,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8793,7 +8801,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8814,13 +8822,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8828,14 +8836,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8854,19 +8862,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8915,7 +8923,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8930,19 +8938,19 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8950,14 +8958,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8976,19 +8984,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9037,7 +9045,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9052,19 +9060,19 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9072,10 +9080,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9098,16 +9106,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9157,7 +9165,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9178,13 +9186,13 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9192,10 +9200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9218,19 +9226,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9279,7 +9287,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9294,19 +9302,19 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9314,10 +9322,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9340,19 +9348,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9389,17 +9397,17 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9408,7 +9416,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9417,30 +9425,30 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>83</v>
@@ -9462,19 +9470,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9523,7 +9531,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9532,7 +9540,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9541,30 +9549,30 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
@@ -9589,16 +9597,16 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9647,7 +9655,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9656,7 +9664,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9665,30 +9673,30 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>83</v>
@@ -9713,16 +9721,16 @@
         <v>162</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9771,7 +9779,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9780,7 +9788,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9789,27 +9797,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9835,16 +9843,16 @@
         <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9872,10 +9880,10 @@
         <v>189</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9893,7 +9901,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9902,7 +9910,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9917,7 +9925,7 @@
         <v>137</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9928,14 +9936,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9957,16 +9965,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9994,10 +10002,10 @@
         <v>189</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -10015,7 +10023,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10033,27 +10041,27 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10076,19 +10084,19 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10137,7 +10145,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10158,10 +10166,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10172,10 +10180,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10290,10 +10298,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10410,10 +10418,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10436,16 +10444,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10495,7 +10503,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10519,7 +10527,7 @@
         <v>137</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10530,10 +10538,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10556,13 +10564,13 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10613,7 +10621,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10637,7 +10645,7 @@
         <v>137</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10648,10 +10656,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10674,16 +10682,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10733,7 +10741,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -10757,7 +10765,7 @@
         <v>137</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10768,10 +10776,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10797,13 +10805,13 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10829,13 +10837,13 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10853,7 +10861,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10871,27 +10879,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10917,16 +10925,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10951,13 +10959,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10975,7 +10983,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10996,10 +11004,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11010,10 +11018,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11036,16 +11044,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11095,7 +11103,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11113,27 +11121,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11156,16 +11164,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11215,7 +11223,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11233,27 +11241,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11276,19 +11284,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11337,7 +11345,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11349,7 +11357,7 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
@@ -11358,10 +11366,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11372,10 +11380,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11490,10 +11498,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11610,14 +11618,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11639,10 +11647,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -11697,7 +11705,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11732,10 +11740,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11758,16 +11766,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11817,7 +11825,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11826,7 +11834,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11838,10 +11846,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11852,10 +11860,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11878,16 +11886,16 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11937,7 +11945,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11946,7 +11954,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11958,10 +11966,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11972,10 +11980,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12001,16 +12009,16 @@
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12038,10 +12046,10 @@
         <v>118</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12059,7 +12067,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12077,13 +12085,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12094,10 +12102,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12123,16 +12131,16 @@
         <v>184</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12157,13 +12165,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12181,7 +12189,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12199,13 +12207,13 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12216,10 +12224,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12242,19 +12250,19 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12303,7 +12311,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12327,7 +12335,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12338,10 +12346,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12367,13 +12375,13 @@
         <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12423,7 +12431,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12444,10 +12452,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12458,10 +12466,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12484,16 +12492,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12543,7 +12551,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12564,10 +12572,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12578,10 +12586,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12604,16 +12612,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12663,7 +12671,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12684,10 +12692,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12698,10 +12706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12724,19 +12732,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12785,7 +12793,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12806,10 +12814,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12820,10 +12828,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12938,10 +12946,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13058,14 +13066,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13087,10 +13095,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>143</v>
@@ -13145,7 +13153,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13180,10 +13188,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13209,16 +13217,16 @@
         <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13243,13 +13251,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13267,7 +13275,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13285,16 +13293,16 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -13302,10 +13310,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13328,19 +13336,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13389,7 +13397,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13407,27 +13415,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13453,16 +13461,16 @@
         <v>184</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13490,10 +13498,10 @@
         <v>189</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13511,7 +13519,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13520,7 +13528,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13535,7 +13543,7 @@
         <v>137</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13546,14 +13554,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13575,16 +13583,16 @@
         <v>184</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13612,10 +13620,10 @@
         <v>189</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13633,7 +13641,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13651,27 +13659,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13697,16 +13705,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13755,7 +13763,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13776,10 +13784,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -1653,10 +1653,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -10839,11 +10836,9 @@
       <c r="X70" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Y70" t="s" s="2">
+      <c r="Y70" s="2"/>
+      <c r="Z70" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10879,27 +10874,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10925,16 +10920,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10962,11 +10957,11 @@
         <v>515</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10983,7 +10978,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11004,10 +10999,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11018,10 +11013,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11044,16 +11039,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11103,7 +11098,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11121,27 +11116,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>539</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11164,16 +11159,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11223,7 +11218,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11241,27 +11236,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>548</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11284,19 +11279,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11345,7 +11340,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11357,19 +11352,19 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AK74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11380,10 +11375,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11498,10 +11493,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11618,14 +11613,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11647,10 +11642,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -11705,7 +11700,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11740,10 +11735,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11766,16 +11761,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11825,7 +11820,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11834,7 +11829,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11846,10 +11841,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11860,10 +11855,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11886,16 +11881,16 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>575</v>
-      </c>
       <c r="N79" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11945,7 +11940,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11954,7 +11949,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11966,10 +11961,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11980,10 +11975,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12009,16 +12004,16 @@
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12046,11 +12041,11 @@
         <v>118</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>583</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12067,7 +12062,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12085,10 +12080,10 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>480</v>
@@ -12102,10 +12097,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12131,16 +12126,16 @@
         <v>184</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12168,11 +12163,11 @@
         <v>515</v>
       </c>
       <c r="Y81" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z81" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z81" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
       </c>
@@ -12189,7 +12184,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12207,10 +12202,10 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>480</v>
@@ -12224,10 +12219,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12250,19 +12245,19 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12311,7 +12306,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12335,7 +12330,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12346,10 +12341,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12375,10 +12370,10 @@
         <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>371</v>
@@ -12431,7 +12426,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12452,10 +12447,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12466,10 +12461,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12492,16 +12487,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12551,7 +12546,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12572,10 +12567,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12586,10 +12581,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12612,16 +12607,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12671,7 +12666,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12692,10 +12687,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12706,10 +12701,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12732,19 +12727,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12793,7 +12788,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12814,10 +12809,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12828,10 +12823,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12946,10 +12941,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13066,14 +13061,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13095,10 +13090,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>143</v>
@@ -13153,7 +13148,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13188,10 +13183,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13217,13 +13212,13 @@
         <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>346</v>
@@ -13254,11 +13249,11 @@
         <v>515</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>632</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
       </c>
@@ -13275,7 +13270,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13293,7 +13288,7 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>351</v>
@@ -13310,10 +13305,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13336,16 +13331,16 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>439</v>
@@ -13397,7 +13392,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13415,7 +13410,7 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>444</v>
@@ -13432,10 +13427,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13461,13 +13456,13 @@
         <v>184</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>465</v>
@@ -13519,7 +13514,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13554,10 +13549,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13583,16 +13578,16 @@
         <v>184</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13641,7 +13636,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13676,10 +13671,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13705,16 +13700,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13763,7 +13758,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13784,10 +13779,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1494,7 +1494,7 @@
     <t>多くの結果には、測定で例外的な値を処理する必要があります。 / For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1773,7 +1773,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -2054,7 +2054,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -1847,7 +1847,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>対象となる母集団のどの部分に適用するかを示すコード。正常範囲、要治療範囲、など。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -909,7 +909,7 @@
     <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表から"laboratory"を設定する。</t>
   </si>
   <si>
-    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「furst」固定とする。  
+    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「laboratory」固定とする。  
 (social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
   </si>
   <si>
@@ -1292,7 +1292,7 @@
 PeriodTiming</t>
   </si>
   <si>
-    <t>取得された結果が臨床的に確定された日時または期間</t>
+    <t>検体を採取した日時または期間</t>
   </si>
   <si>
     <t>検体検査の場合は、検体採取日時。</t>
@@ -1381,7 +1381,7 @@
 CodeableConceptstring</t>
   </si>
   <si>
-    <t>同じ検査項目でも、システム（施設）により、使うデータ型が異なる可能性あり【詳細参照】</t>
+    <t>検体検査結果の値</t>
   </si>
   <si>
     <t>検体検査の結果として決定された情報。</t>
@@ -5711,7 +5711,7 @@
         <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -2392,15 +2392,15 @@
   <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2411,28 +2411,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.09375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -1653,7 +1653,10 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -10836,9 +10839,11 @@
       <c r="X70" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Y70" s="2"/>
+      <c r="Y70" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10874,27 +10879,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10920,16 +10925,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10957,10 +10962,10 @@
         <v>515</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10978,7 +10983,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10999,10 +11004,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11013,10 +11018,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11039,16 +11044,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11098,7 +11103,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11116,27 +11121,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11159,16 +11164,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11218,7 +11223,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11236,27 +11241,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11279,19 +11284,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11340,7 +11345,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11352,7 +11357,7 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
@@ -11361,10 +11366,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11375,10 +11380,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11493,10 +11498,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11613,14 +11618,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11642,10 +11647,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -11700,7 +11705,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11735,10 +11740,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11761,16 +11766,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11820,7 +11825,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11829,7 +11834,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11841,10 +11846,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11855,10 +11860,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11881,16 +11886,16 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11940,7 +11945,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11949,7 +11954,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11961,10 +11966,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11975,10 +11980,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12004,16 +12009,16 @@
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12041,10 +12046,10 @@
         <v>118</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12062,7 +12067,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12080,10 +12085,10 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>480</v>
@@ -12097,10 +12102,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12126,16 +12131,16 @@
         <v>184</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12163,10 +12168,10 @@
         <v>515</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12184,7 +12189,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12202,10 +12207,10 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>480</v>
@@ -12219,10 +12224,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12245,19 +12250,19 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12306,7 +12311,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12330,7 +12335,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12341,10 +12346,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12370,10 +12375,10 @@
         <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>371</v>
@@ -12426,7 +12431,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12447,10 +12452,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12461,10 +12466,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12487,16 +12492,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12546,7 +12551,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12567,10 +12572,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12581,10 +12586,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12607,16 +12612,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12666,7 +12671,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12687,10 +12692,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12701,10 +12706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12727,19 +12732,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12788,7 +12793,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12809,10 +12814,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12823,10 +12828,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12941,10 +12946,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13061,14 +13066,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13090,10 +13095,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>143</v>
@@ -13148,7 +13153,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13183,10 +13188,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13212,13 +13217,13 @@
         <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>346</v>
@@ -13249,10 +13254,10 @@
         <v>515</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13270,7 +13275,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13288,7 +13293,7 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>351</v>
@@ -13305,10 +13310,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13331,16 +13336,16 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>439</v>
@@ -13392,7 +13397,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13410,7 +13415,7 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>444</v>
@@ -13427,10 +13432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13456,13 +13461,13 @@
         <v>184</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>465</v>
@@ -13514,7 +13519,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13549,10 +13554,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13578,16 +13583,16 @@
         <v>184</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13636,7 +13641,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13671,10 +13676,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13700,16 +13705,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13758,7 +13763,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13779,10 +13784,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -618,7 +618,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -697,7 +697,7 @@
     <t>Observation.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -832,7 +832,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1232,7 +1232,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1497,7 +1497,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1531,7 +1531,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1581,7 +1581,7 @@
     <t>Observation.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1656,7 +1656,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1691,7 +1691,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1731,7 +1731,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1812,7 +1812,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1865,7 +1865,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1898,7 +1898,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2021,7 +2021,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR 
--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -835,7 +835,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3646" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -1173,9 +1173,6 @@
     <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Observation.code.coding.display</t>
   </si>
   <si>
@@ -1259,7 +1256,7 @@
     <t>診察や入院など、このObservationが実施されるきっかけとなった診療イベントに関する情報</t>
   </si>
   <si>
-    <t>この検査が行われるヘルスケアイベント。医療提供者と患者の接点。</t>
+    <t>この検査が行われる診療イベント。医療提供者と患者の接点。</t>
   </si>
   <si>
     <t>【JP Core仕様】入院外来の区別や所在場所、担当診療科の情報に使用する。  
@@ -8140,9 +8137,7 @@
       <c r="M48" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>317</v>
       </c>
@@ -8228,10 +8223,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8262,9 +8257,7 @@
       <c r="M49" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>326</v>
       </c>
@@ -8350,10 +8343,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8382,10 +8375,10 @@
         <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>336</v>
@@ -8472,10 +8465,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8504,10 +8497,10 @@
         <v>275</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O51" t="s" s="2">
         <v>278</v>
@@ -8594,10 +8587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8620,19 +8613,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8681,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8696,19 +8689,19 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8716,10 +8709,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8742,16 +8735,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8801,7 +8794,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8825,10 +8818,10 @@
         <v>351</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8836,14 +8829,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8862,19 +8855,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8923,7 +8916,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8938,19 +8931,19 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8958,14 +8951,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8984,19 +8977,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9045,7 +9038,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9060,19 +9053,19 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9080,10 +9073,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9106,16 +9099,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9165,7 +9158,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9186,13 +9179,13 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9200,10 +9193,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9226,19 +9219,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9287,7 +9280,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9302,19 +9295,19 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9322,10 +9315,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9348,19 +9341,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9397,17 +9390,17 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9416,7 +9409,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9425,30 +9418,30 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>83</v>
@@ -9470,19 +9463,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="N59" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9531,7 +9524,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9540,7 +9533,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9549,30 +9542,30 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
@@ -9597,16 +9590,16 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>456</v>
-      </c>
       <c r="O60" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9655,7 +9648,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9664,7 +9657,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9673,30 +9666,30 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>83</v>
@@ -9721,16 +9714,16 @@
         <v>162</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="O61" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9779,7 +9772,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9788,7 +9781,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9797,27 +9790,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9843,16 +9836,16 @@
         <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9880,11 +9873,11 @@
         <v>189</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9901,7 +9894,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9910,7 +9903,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9925,7 +9918,7 @@
         <v>137</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9936,14 +9929,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9965,16 +9958,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10002,11 +9995,11 @@
         <v>189</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
       </c>
@@ -10023,7 +10016,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10041,27 +10034,27 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10084,19 +10077,19 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10145,7 +10138,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10166,10 +10159,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10180,10 +10173,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10298,10 +10291,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10418,10 +10411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10444,16 +10437,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10503,7 +10496,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10527,7 +10520,7 @@
         <v>137</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10538,10 +10531,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10564,13 +10557,13 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10621,7 +10614,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10645,7 +10638,7 @@
         <v>137</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10656,10 +10649,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10682,16 +10675,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10741,7 +10734,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -10765,7 +10758,7 @@
         <v>137</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10776,10 +10769,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10805,13 +10798,13 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="N70" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10837,14 +10830,14 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Y70" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Y70" t="s" s="2">
+      <c r="Z70" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
       </c>
@@ -10861,7 +10854,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10879,27 +10872,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10925,16 +10918,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10959,14 +10952,14 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10983,7 +10976,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11004,10 +10997,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11018,10 +11011,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11044,16 +11037,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11103,7 +11096,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11121,27 +11114,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>539</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11164,16 +11157,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11223,7 +11216,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11241,27 +11234,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>548</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11284,19 +11277,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11345,7 +11338,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11357,19 +11350,19 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AK74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11380,10 +11373,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11498,10 +11491,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11618,14 +11611,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11647,10 +11640,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -11705,7 +11698,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11740,10 +11733,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11766,16 +11759,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11825,7 +11818,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11834,7 +11827,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11846,10 +11839,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11860,10 +11853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11886,16 +11879,16 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>575</v>
-      </c>
       <c r="N79" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11945,7 +11938,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11954,7 +11947,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11966,10 +11959,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11980,10 +11973,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12009,16 +12002,16 @@
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12046,11 +12039,11 @@
         <v>118</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>583</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12067,7 +12060,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12085,13 +12078,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AM80" t="s" s="2">
-        <v>585</v>
-      </c>
       <c r="AN80" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12102,10 +12095,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12131,16 +12124,16 @@
         <v>184</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12165,14 +12158,14 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y81" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z81" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z81" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
       </c>
@@ -12189,7 +12182,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12207,13 +12200,13 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AM81" t="s" s="2">
-        <v>585</v>
-      </c>
       <c r="AN81" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12224,10 +12217,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12250,19 +12243,19 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12311,7 +12304,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12335,7 +12328,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12346,10 +12339,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12375,14 +12368,12 @@
         <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12431,7 +12422,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12452,10 +12443,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12466,10 +12457,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12492,16 +12483,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12551,7 +12542,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12572,10 +12563,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12586,10 +12577,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12612,16 +12603,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12671,7 +12662,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12692,10 +12683,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12706,10 +12697,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12732,19 +12723,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12793,7 +12784,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12814,10 +12805,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12828,10 +12819,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12946,10 +12937,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13066,14 +13057,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13095,10 +13086,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>143</v>
@@ -13153,7 +13144,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13188,10 +13179,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13217,13 +13208,13 @@
         <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>346</v>
@@ -13251,14 +13242,14 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>632</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
       </c>
@@ -13275,7 +13266,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13293,7 +13284,7 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>351</v>
@@ -13310,10 +13301,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13336,19 +13327,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="N91" t="s" s="2">
-        <v>638</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13397,7 +13388,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13415,27 +13406,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP91" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13461,16 +13452,16 @@
         <v>184</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N92" t="s" s="2">
-        <v>643</v>
-      </c>
       <c r="O92" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13498,11 +13489,11 @@
         <v>189</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13519,7 +13510,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13528,7 +13519,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13543,7 +13534,7 @@
         <v>137</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13554,14 +13545,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13583,16 +13574,16 @@
         <v>184</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13620,11 +13611,11 @@
         <v>189</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13641,7 +13632,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13659,27 +13650,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13705,16 +13696,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13763,7 +13754,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13784,10 +13775,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -913,6 +913,14 @@
 (social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="laboratory"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -1007,9 +1015,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>laboratory</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -5745,7 +5750,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>286</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5764,7 +5769,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5817,7 +5822,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>264</v>
@@ -5935,7 +5940,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>265</v>
@@ -6055,7 +6060,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>266</v>
@@ -6084,13 +6089,13 @@
         <v>267</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O31" t="s" s="2">
         <v>270</v>
@@ -6177,10 +6182,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6295,10 +6300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6415,10 +6420,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6444,23 +6449,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6502,7 +6507,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6523,10 +6528,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6537,10 +6542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6566,13 +6571,13 @@
         <v>162</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6622,7 +6627,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6643,10 +6648,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6657,10 +6662,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6686,21 +6691,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -7530,7 +7535,7 @@
         <v>267</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M43" t="s" s="2">
         <v>358</v>
@@ -7899,7 +7904,7 @@
         <v>365</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7948,7 +7953,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7969,10 +7974,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -8012,10 +8017,10 @@
         <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>367</v>
@@ -8068,7 +8073,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8089,10 +8094,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8139,7 +8144,7 @@
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -502,11 +502,11 @@
 アプリケーション側のデータベースにおけるフィールド長の定義については、最低64バイトを確保すること。  
 --- 参考 ---  
 次の項目を順にセパレータ「_(アンダースコア)」で連結し、 identifier.value に設定する。グループ項目でない場合など、該当コード／番号がない場合はセパレータを連続で連結する。各コードはローカルコードを使用し、必ず設定できること。  
-　１．ORC-2(依頼者オーダ番号)　SS-MIX2の15桁前ゼロ形式の番号  
-　２．OBR-4(検査項目ID)　検査セットの識別コード  
-　３．SPM-4(検体タイプ)  
-　４．OBX-3(検査項目)  
-　５．OBX-4(検査副ID)・・・オプション。必要に応じて使用。  
+　１、ORC-2(依頼者オーダ番号)　SS-MIX2の15桁前ゼロ形式の番号  
+　２、OBR-4(検査項目ID)　検査セットの識別コード  
+　３、SPM-4(検体タイプ)  
+　４、OBX-3(検査項目)  
+　５、OBX-4(検査副ID)・・・オプション。必要に応じて使用。  
 形式：[ORC-2]_[OBR-4]_[SPM-4]_[OBX-3]（_[OBX-4]）</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-labresult.xlsx
@@ -758,7 +758,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -1990,7 +1990,7 @@
     <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](observation.html#notes) below.</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
